--- a/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1656_W0034F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.3361847471211</v>
+        <v>11.75463002140718</v>
       </c>
       <c r="D2" t="n">
-        <v>66.32894159119253</v>
+        <v>10.77845300856879</v>
       </c>
       <c r="E2" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F2" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>102.8855520751094</v>
+        <v>16.71890221220528</v>
       </c>
       <c r="D3" t="n">
-        <v>72.06612559210487</v>
+        <v>11.71074540871704</v>
       </c>
       <c r="E3" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F3" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>64.1480169087386</v>
+        <v>10.42405274767002</v>
       </c>
       <c r="D4" t="n">
-        <v>64.59094727412163</v>
+        <v>10.49602893204477</v>
       </c>
       <c r="E4" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F4" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>85.73295025878991</v>
+        <v>13.93160441705336</v>
       </c>
       <c r="D5" t="n">
-        <v>55.09694921293982</v>
+        <v>8.953254247102722</v>
       </c>
       <c r="E5" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F5" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>14.64748246426937</v>
+        <v>2.380215900443772</v>
       </c>
       <c r="D6" t="n">
-        <v>16.81648868864542</v>
+        <v>2.732679411904881</v>
       </c>
       <c r="E6" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F6" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.62254575556167</v>
+        <v>4.651163685278771</v>
       </c>
       <c r="D7" t="n">
-        <v>19.29755238384771</v>
+        <v>3.135852262375253</v>
       </c>
       <c r="E7" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F7" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.21348436338592</v>
+        <v>6.372191209050213</v>
       </c>
       <c r="D8" t="n">
-        <v>18.55697855232508</v>
+        <v>3.015509014752826</v>
       </c>
       <c r="E8" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F8" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>34.6674758463259</v>
+        <v>5.633464825027959</v>
       </c>
       <c r="D9" t="n">
-        <v>6.530297567859085</v>
+        <v>1.061173354777101</v>
       </c>
       <c r="E9" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F9" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>65.55289873658403</v>
+        <v>10.65234604469491</v>
       </c>
       <c r="D10" t="n">
-        <v>11.65715167752306</v>
+        <v>1.894287147597497</v>
       </c>
       <c r="E10" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F10" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.21529059176818</v>
+        <v>4.09748472116233</v>
       </c>
       <c r="D11" t="n">
-        <v>17.67210308392492</v>
+        <v>2.871716751137799</v>
       </c>
       <c r="E11" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F11" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>36.03737920097267</v>
+        <v>5.85607412015806</v>
       </c>
       <c r="D12" t="n">
-        <v>34.3091921085419</v>
+        <v>5.575243717638059</v>
       </c>
       <c r="E12" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F12" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.54164442582476</v>
+        <v>6.588017219196523</v>
       </c>
       <c r="D13" t="n">
-        <v>24.01984154337364</v>
+        <v>3.903224250798216</v>
       </c>
       <c r="E13" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F13" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>58.65475106673048</v>
+        <v>9.531397048343704</v>
       </c>
       <c r="D14" t="n">
-        <v>54.18410812031599</v>
+        <v>8.804917569551348</v>
       </c>
       <c r="E14" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F14" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>54.90751845691238</v>
+        <v>8.922471749248261</v>
       </c>
       <c r="D15" t="n">
-        <v>52.99682089367523</v>
+        <v>8.611983395222225</v>
       </c>
       <c r="E15" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F15" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>75.11274518077268</v>
+        <v>12.20582109187556</v>
       </c>
       <c r="D16" t="n">
-        <v>73.38285326985471</v>
+        <v>11.92471365635139</v>
       </c>
       <c r="E16" t="n">
-        <v>23.86892729871635</v>
+        <v>3.878700686041407</v>
       </c>
       <c r="F16" t="n">
-        <v>23.32936732805532</v>
+        <v>3.79102219080899</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
